--- a/sport_schema.xlsx
+++ b/sport_schema.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gtisc\sport_app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE5D3D77-6977-4330-84EE-7F353894937D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{54931908-260D-47D7-A974-BEC8ED36FA53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{D4084558-AAF6-47C4-B3D2-14E9813C2DBA}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="24">
   <si>
     <t>wat te doen</t>
   </si>
@@ -53,9 +53,6 @@
     <t>rust</t>
   </si>
   <si>
-    <t xml:space="preserve">https://youtu.be/uQK5r57UxR4?si=flHallRFEcoV7R6R </t>
-  </si>
-  <si>
     <t>https://youtu.be/27IXyMaDYgQ?si=VJEs3o-bQ914QQ3W</t>
   </si>
   <si>
@@ -63,9 +60,6 @@
   </si>
   <si>
     <t>https://youtu.be/riRy-9Nh3p4?si=zf2hVY0vLah5WkxA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://youtu.be/riRy-9Nh3p4?si=zf2hVY0vLah5WkxA </t>
   </si>
   <si>
     <t>https://youtu.be/dcycxA9xZC4?si=3sCNT6CuPpOnkmVm</t>
@@ -548,14 +542,14 @@
   <cols>
     <col min="1" max="1" width="21.5546875" customWidth="1"/>
     <col min="2" max="2" width="14.88671875" customWidth="1"/>
-    <col min="3" max="3" width="46.5546875" customWidth="1"/>
+    <col min="3" max="3" width="48.33203125" customWidth="1"/>
     <col min="4" max="4" width="49.88671875" customWidth="1"/>
     <col min="5" max="5" width="12.109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -570,76 +564,76 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E2" s="5"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D3" s="4"/>
       <c r="E3" s="6"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>3</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E4" s="6"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D5" s="4" t="s">
         <v>7</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>9</v>
       </c>
       <c r="E5" s="6"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>3</v>
       </c>
       <c r="C6" s="3"/>
       <c r="D6" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E6" s="6"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>4</v>
@@ -650,7 +644,7 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>4</v>
@@ -661,70 +655,70 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E9" s="6"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="6"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>3</v>
       </c>
       <c r="C11" s="3"/>
       <c r="D11" s="4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E11" s="6"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C12" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D12" s="4" t="s">
         <v>7</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>8</v>
       </c>
       <c r="E12" s="6"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>3</v>
       </c>
       <c r="C13" s="3"/>
       <c r="D13" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E13" s="6"/>
     </row>
